--- a/Team-Data/2008-09/4-15-2008-09.xlsx
+++ b/Team-Data/2008-09/4-15-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,40 +728,40 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E2" t="n">
         <v>47</v>
       </c>
       <c r="F2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G2" t="n">
-        <v>0.573</v>
+        <v>0.58</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
       </c>
       <c r="I2" t="n">
-        <v>36</v>
+        <v>36.1</v>
       </c>
       <c r="J2" t="n">
         <v>78.7</v>
       </c>
       <c r="K2" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="L2" t="n">
         <v>7.3</v>
       </c>
       <c r="M2" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="N2" t="n">
         <v>0.366</v>
       </c>
       <c r="O2" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="P2" t="n">
         <v>25.4</v>
@@ -712,7 +779,7 @@
         <v>40</v>
       </c>
       <c r="U2" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="V2" t="n">
         <v>12.8</v>
@@ -724,28 +791,28 @@
         <v>4.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>98.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
       </c>
       <c r="AF2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG2" t="n">
         <v>12</v>
@@ -757,16 +824,16 @@
         <v>24</v>
       </c>
       <c r="AJ2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL2" t="n">
         <v>8</v>
       </c>
       <c r="AM2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN2" t="n">
         <v>16</v>
@@ -790,19 +857,19 @@
         <v>23</v>
       </c>
       <c r="AU2" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AV2" t="n">
         <v>7</v>
       </c>
       <c r="AW2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AX2" t="n">
         <v>20</v>
       </c>
       <c r="AY2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ2" t="n">
         <v>5</v>
@@ -811,7 +878,7 @@
         <v>17</v>
       </c>
       <c r="BB2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC2" t="n">
         <v>12</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-15-2008-09</t>
+          <t>2009-04-15</t>
         </is>
       </c>
     </row>
@@ -858,31 +925,31 @@
         <v>48.5</v>
       </c>
       <c r="I3" t="n">
-        <v>37.6</v>
+        <v>37.4</v>
       </c>
       <c r="J3" t="n">
-        <v>77.3</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.486</v>
+        <v>0.485</v>
       </c>
       <c r="L3" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0.399</v>
+        <v>0.395</v>
       </c>
       <c r="O3" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="P3" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.767</v>
+        <v>0.766</v>
       </c>
       <c r="R3" t="n">
         <v>10.6</v>
@@ -891,22 +958,22 @@
         <v>31.6</v>
       </c>
       <c r="T3" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="U3" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="V3" t="n">
         <v>15.6</v>
       </c>
       <c r="W3" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X3" t="n">
         <v>4.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z3" t="n">
         <v>23.1</v>
@@ -915,13 +982,13 @@
         <v>22.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>101</v>
+        <v>100.7</v>
       </c>
       <c r="AC3" t="n">
         <v>7.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
         <v>3</v>
@@ -933,7 +1000,7 @@
         <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AI3" t="n">
         <v>9</v>
@@ -945,7 +1012,7 @@
         <v>2</v>
       </c>
       <c r="AL3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM3" t="n">
         <v>21</v>
@@ -957,7 +1024,7 @@
         <v>12</v>
       </c>
       <c r="AP3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AQ3" t="n">
         <v>16</v>
@@ -969,7 +1036,7 @@
         <v>6</v>
       </c>
       <c r="AT3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU3" t="n">
         <v>4</v>
@@ -978,10 +1045,10 @@
         <v>27</v>
       </c>
       <c r="AW3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY3" t="n">
         <v>13</v>
@@ -990,13 +1057,13 @@
         <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-15-2008-09</t>
+          <t>2009-04-15</t>
         </is>
       </c>
     </row>
@@ -1025,58 +1092,58 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E4" t="n">
         <v>35</v>
       </c>
       <c r="F4" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G4" t="n">
-        <v>0.427</v>
+        <v>0.432</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
       </c>
       <c r="I4" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="J4" t="n">
-        <v>76.8</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L4" t="n">
         <v>6</v>
       </c>
       <c r="M4" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="N4" t="n">
-        <v>0.366</v>
+        <v>0.368</v>
       </c>
       <c r="O4" t="n">
         <v>17.7</v>
       </c>
       <c r="P4" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.74</v>
+        <v>0.742</v>
       </c>
       <c r="R4" t="n">
         <v>10.8</v>
       </c>
       <c r="S4" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="T4" t="n">
-        <v>39.7</v>
+        <v>39.6</v>
       </c>
       <c r="U4" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V4" t="n">
         <v>15.6</v>
@@ -1097,25 +1164,25 @@
         <v>20.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>93.59999999999999</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1.3</v>
+        <v>-1</v>
       </c>
       <c r="AD4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH4" t="n">
         <v>1</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>3</v>
       </c>
       <c r="AI4" t="n">
         <v>29</v>
@@ -1133,7 +1200,7 @@
         <v>22</v>
       </c>
       <c r="AN4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO4" t="n">
         <v>26</v>
@@ -1145,10 +1212,10 @@
         <v>27</v>
       </c>
       <c r="AR4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT4" t="n">
         <v>27</v>
@@ -1175,10 +1242,10 @@
         <v>13</v>
       </c>
       <c r="BB4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-15-2008-09</t>
+          <t>2009-04-15</t>
         </is>
       </c>
     </row>
@@ -1210,25 +1277,25 @@
         <v>81</v>
       </c>
       <c r="E5" t="n">
+        <v>41</v>
+      </c>
+      <c r="F5" t="n">
         <v>40</v>
       </c>
-      <c r="F5" t="n">
-        <v>41</v>
-      </c>
       <c r="G5" t="n">
-        <v>0.494</v>
+        <v>0.506</v>
       </c>
       <c r="H5" t="n">
         <v>48.6</v>
       </c>
       <c r="I5" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J5" t="n">
-        <v>83.7</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L5" t="n">
         <v>6</v>
@@ -1237,16 +1304,16 @@
         <v>15.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0.381</v>
+        <v>0.383</v>
       </c>
       <c r="O5" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="P5" t="n">
-        <v>24.8</v>
+        <v>25.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.797</v>
+        <v>0.796</v>
       </c>
       <c r="R5" t="n">
         <v>11.8</v>
@@ -1258,10 +1325,10 @@
         <v>42.1</v>
       </c>
       <c r="U5" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="V5" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W5" t="n">
         <v>7.5</v>
@@ -1276,37 +1343,37 @@
         <v>20.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>102.1</v>
+        <v>102.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF5" t="n">
         <v>15</v>
       </c>
       <c r="AG5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ5" t="n">
         <v>5</v>
       </c>
       <c r="AK5" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AL5" t="n">
         <v>22</v>
@@ -1315,10 +1382,10 @@
         <v>23</v>
       </c>
       <c r="AN5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AO5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP5" t="n">
         <v>14</v>
@@ -1327,22 +1394,22 @@
         <v>7</v>
       </c>
       <c r="AR5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS5" t="n">
         <v>15</v>
       </c>
       <c r="AT5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU5" t="n">
         <v>13</v>
       </c>
       <c r="AV5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX5" t="n">
         <v>4</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-15-2008-09</t>
+          <t>2009-04-15</t>
         </is>
       </c>
     </row>
@@ -1404,46 +1471,46 @@
         <v>48.2</v>
       </c>
       <c r="I6" t="n">
-        <v>37</v>
+        <v>36.7</v>
       </c>
       <c r="J6" t="n">
-        <v>78.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.469</v>
+        <v>0.468</v>
       </c>
       <c r="L6" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="M6" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0.395</v>
+        <v>0.392</v>
       </c>
       <c r="O6" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
       <c r="P6" t="n">
-        <v>24.4</v>
+        <v>24.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.757</v>
+        <v>0.758</v>
       </c>
       <c r="R6" t="n">
         <v>10.8</v>
       </c>
       <c r="S6" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="T6" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="U6" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V6" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="W6" t="n">
         <v>7.2</v>
@@ -1452,22 +1519,22 @@
         <v>5.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.5</v>
+        <v>100.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="AD6" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1479,19 +1546,19 @@
         <v>1</v>
       </c>
       <c r="AH6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK6" t="n">
         <v>6</v>
       </c>
       <c r="AL6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM6" t="n">
         <v>5</v>
@@ -1500,7 +1567,7 @@
         <v>2</v>
       </c>
       <c r="AO6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AP6" t="n">
         <v>15</v>
@@ -1509,7 +1576,7 @@
         <v>21</v>
       </c>
       <c r="AR6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS6" t="n">
         <v>8</v>
@@ -1518,7 +1585,7 @@
         <v>7</v>
       </c>
       <c r="AU6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AV6" t="n">
         <v>5</v>
@@ -1530,10 +1597,10 @@
         <v>7</v>
       </c>
       <c r="AY6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>7</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>9</v>
       </c>
       <c r="BA6" t="n">
         <v>20</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-15-2008-09</t>
+          <t>2009-04-15</t>
         </is>
       </c>
     </row>
@@ -1571,22 +1638,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F7" t="n">
         <v>32</v>
       </c>
       <c r="G7" t="n">
-        <v>0.61</v>
+        <v>0.605</v>
       </c>
       <c r="H7" t="n">
         <v>48.3</v>
       </c>
       <c r="I7" t="n">
-        <v>38.1</v>
+        <v>38.2</v>
       </c>
       <c r="J7" t="n">
         <v>82.59999999999999</v>
@@ -1598,10 +1665,10 @@
         <v>7</v>
       </c>
       <c r="M7" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="N7" t="n">
-        <v>0.35</v>
+        <v>0.349</v>
       </c>
       <c r="O7" t="n">
         <v>18.5</v>
@@ -1619,7 +1686,7 @@
         <v>31.6</v>
       </c>
       <c r="T7" t="n">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="U7" t="n">
         <v>21.7</v>
@@ -1628,13 +1695,13 @@
         <v>12.7</v>
       </c>
       <c r="W7" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X7" t="n">
         <v>5.2</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z7" t="n">
         <v>19.5</v>
@@ -1643,13 +1710,13 @@
         <v>20.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>101.7</v>
+        <v>101.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
         <v>9</v>
@@ -1664,7 +1731,7 @@
         <v>14</v>
       </c>
       <c r="AI7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ7" t="n">
         <v>6</v>
@@ -1676,13 +1743,13 @@
         <v>12</v>
       </c>
       <c r="AM7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN7" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AO7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP7" t="n">
         <v>26</v>
@@ -1691,7 +1758,7 @@
         <v>2</v>
       </c>
       <c r="AR7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS7" t="n">
         <v>5</v>
@@ -1706,10 +1773,10 @@
         <v>6</v>
       </c>
       <c r="AW7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AX7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY7" t="n">
         <v>4</v>
@@ -1718,13 +1785,13 @@
         <v>4</v>
       </c>
       <c r="BA7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB7" t="n">
         <v>9</v>
       </c>
       <c r="BC7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-15-2008-09</t>
+          <t>2009-04-15</t>
         </is>
       </c>
     </row>
@@ -1753,28 +1820,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E8" t="n">
         <v>54</v>
       </c>
       <c r="F8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G8" t="n">
-        <v>0.659</v>
+        <v>0.667</v>
       </c>
       <c r="H8" t="n">
         <v>48.1</v>
       </c>
       <c r="I8" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="J8" t="n">
-        <v>79.40000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="K8" t="n">
-        <v>0.47</v>
+        <v>0.471</v>
       </c>
       <c r="L8" t="n">
         <v>6.7</v>
@@ -1783,16 +1850,16 @@
         <v>18</v>
       </c>
       <c r="N8" t="n">
-        <v>0.371</v>
+        <v>0.372</v>
       </c>
       <c r="O8" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="P8" t="n">
-        <v>30.3</v>
+        <v>30.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.76</v>
+        <v>0.759</v>
       </c>
       <c r="R8" t="n">
         <v>11</v>
@@ -1804,7 +1871,7 @@
         <v>41.6</v>
       </c>
       <c r="U8" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="V8" t="n">
         <v>15.3</v>
@@ -1822,31 +1889,31 @@
         <v>22.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>104.3</v>
+        <v>104.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
       </c>
       <c r="AF8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH8" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ8" t="n">
         <v>22</v>
@@ -1861,10 +1928,10 @@
         <v>17</v>
       </c>
       <c r="AN8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP8" t="n">
         <v>1</v>
@@ -1876,16 +1943,16 @@
         <v>15</v>
       </c>
       <c r="AS8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW8" t="n">
         <v>3</v>
@@ -1906,7 +1973,7 @@
         <v>6</v>
       </c>
       <c r="BC8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-15-2008-09</t>
+          <t>2009-04-15</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E9" t="n">
         <v>39</v>
       </c>
       <c r="F9" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G9" t="n">
-        <v>0.476</v>
+        <v>0.481</v>
       </c>
       <c r="H9" t="n">
         <v>48.5</v>
@@ -1953,10 +2020,10 @@
         <v>36.4</v>
       </c>
       <c r="J9" t="n">
-        <v>80</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.454</v>
+        <v>0.455</v>
       </c>
       <c r="L9" t="n">
         <v>4.6</v>
@@ -1965,19 +2032,19 @@
         <v>13.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0.349</v>
+        <v>0.352</v>
       </c>
       <c r="O9" t="n">
         <v>16.9</v>
       </c>
       <c r="P9" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="Q9" t="n">
         <v>0.751</v>
       </c>
       <c r="R9" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S9" t="n">
         <v>29.9</v>
@@ -1986,7 +2053,7 @@
         <v>41.4</v>
       </c>
       <c r="U9" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="V9" t="n">
         <v>11.9</v>
@@ -2004,16 +2071,16 @@
         <v>20.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AB9" t="n">
         <v>94.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE9" t="n">
         <v>17</v>
@@ -2025,7 +2092,7 @@
         <v>17</v>
       </c>
       <c r="AH9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI9" t="n">
         <v>22</v>
@@ -2034,7 +2101,7 @@
         <v>17</v>
       </c>
       <c r="AK9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL9" t="n">
         <v>28</v>
@@ -2043,13 +2110,13 @@
         <v>28</v>
       </c>
       <c r="AN9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO9" t="n">
         <v>28</v>
       </c>
       <c r="AP9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ9" t="n">
         <v>24</v>
@@ -2076,13 +2143,13 @@
         <v>19</v>
       </c>
       <c r="AY9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ9" t="n">
         <v>19</v>
       </c>
       <c r="BA9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB9" t="n">
         <v>28</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-15-2008-09</t>
+          <t>2009-04-15</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E10" t="n">
         <v>29</v>
       </c>
       <c r="F10" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G10" t="n">
-        <v>0.354</v>
+        <v>0.358</v>
       </c>
       <c r="H10" t="n">
         <v>48.5</v>
@@ -2147,7 +2214,7 @@
         <v>18</v>
       </c>
       <c r="N10" t="n">
-        <v>0.373</v>
+        <v>0.374</v>
       </c>
       <c r="O10" t="n">
         <v>23.1</v>
@@ -2159,13 +2226,13 @@
         <v>0.791</v>
       </c>
       <c r="R10" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S10" t="n">
         <v>30.4</v>
       </c>
       <c r="T10" t="n">
-        <v>42</v>
+        <v>41.9</v>
       </c>
       <c r="U10" t="n">
         <v>20.9</v>
@@ -2183,19 +2250,19 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="AA10" t="n">
         <v>23.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>108.6</v>
+        <v>108.5</v>
       </c>
       <c r="AC10" t="n">
         <v>-3.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
@@ -2207,7 +2274,7 @@
         <v>24</v>
       </c>
       <c r="AH10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI10" t="n">
         <v>3</v>
@@ -2228,7 +2295,7 @@
         <v>11</v>
       </c>
       <c r="AO10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP10" t="n">
         <v>2</v>
@@ -2240,7 +2307,7 @@
         <v>9</v>
       </c>
       <c r="AS10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT10" t="n">
         <v>11</v>
@@ -2249,7 +2316,7 @@
         <v>15</v>
       </c>
       <c r="AV10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW10" t="n">
         <v>6</v>
@@ -2261,7 +2328,7 @@
         <v>18</v>
       </c>
       <c r="AZ10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA10" t="n">
         <v>3</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-15-2008-09</t>
+          <t>2009-04-15</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E11" t="n">
         <v>53</v>
       </c>
       <c r="F11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G11" t="n">
-        <v>0.646</v>
+        <v>0.654</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
@@ -2320,7 +2387,7 @@
         <v>79.59999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.453</v>
+        <v>0.454</v>
       </c>
       <c r="L11" t="n">
         <v>7.6</v>
@@ -2329,19 +2396,19 @@
         <v>20.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0.375</v>
+        <v>0.376</v>
       </c>
       <c r="O11" t="n">
         <v>18.7</v>
       </c>
       <c r="P11" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="Q11" t="n">
         <v>0.805</v>
       </c>
       <c r="R11" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="S11" t="n">
         <v>32.5</v>
@@ -2353,7 +2420,7 @@
         <v>20.3</v>
       </c>
       <c r="V11" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W11" t="n">
         <v>6.7</v>
@@ -2371,22 +2438,22 @@
         <v>20.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>98.40000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AF11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AG11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AH11" t="n">
         <v>14</v>
@@ -2398,7 +2465,7 @@
         <v>21</v>
       </c>
       <c r="AK11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL11" t="n">
         <v>7</v>
@@ -2407,10 +2474,10 @@
         <v>6</v>
       </c>
       <c r="AN11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AO11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AP11" t="n">
         <v>21</v>
@@ -2428,13 +2495,13 @@
         <v>4</v>
       </c>
       <c r="AU11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AV11" t="n">
         <v>16</v>
       </c>
       <c r="AW11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX11" t="n">
         <v>24</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-15-2008-09</t>
+          <t>2009-04-15</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E12" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F12" t="n">
         <v>46</v>
       </c>
       <c r="G12" t="n">
-        <v>0.439</v>
+        <v>0.432</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
@@ -2499,37 +2566,37 @@
         <v>39.3</v>
       </c>
       <c r="J12" t="n">
-        <v>86.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K12" t="n">
         <v>0.455</v>
       </c>
       <c r="L12" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="M12" t="n">
         <v>21</v>
       </c>
       <c r="N12" t="n">
-        <v>0.378</v>
+        <v>0.376</v>
       </c>
       <c r="O12" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="P12" t="n">
         <v>23</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.806</v>
       </c>
       <c r="R12" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="S12" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="T12" t="n">
-        <v>43.7</v>
+        <v>43.6</v>
       </c>
       <c r="U12" t="n">
         <v>21.6</v>
@@ -2541,25 +2608,25 @@
         <v>7</v>
       </c>
       <c r="X12" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y12" t="n">
         <v>5.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="AA12" t="n">
         <v>20.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>105.1</v>
+        <v>105</v>
       </c>
       <c r="AC12" t="n">
-        <v>-1.1</v>
+        <v>-1.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE12" t="n">
         <v>18</v>
@@ -2571,7 +2638,7 @@
         <v>18</v>
       </c>
       <c r="AH12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI12" t="n">
         <v>4</v>
@@ -2580,25 +2647,25 @@
         <v>2</v>
       </c>
       <c r="AK12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM12" t="n">
         <v>4</v>
       </c>
       <c r="AN12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AO12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AP12" t="n">
         <v>23</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR12" t="n">
         <v>12</v>
@@ -2613,16 +2680,16 @@
         <v>9</v>
       </c>
       <c r="AV12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ12" t="n">
         <v>28</v>
@@ -2634,7 +2701,7 @@
         <v>5</v>
       </c>
       <c r="BC12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-15-2008-09</t>
+          <t>2009-04-15</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E13" t="n">
         <v>19</v>
       </c>
       <c r="F13" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G13" t="n">
-        <v>0.232</v>
+        <v>0.235</v>
       </c>
       <c r="H13" t="n">
         <v>48.5</v>
@@ -2690,16 +2757,16 @@
         <v>6.5</v>
       </c>
       <c r="M13" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="N13" t="n">
-        <v>0.354</v>
+        <v>0.355</v>
       </c>
       <c r="O13" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="P13" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="Q13" t="n">
         <v>0.736</v>
@@ -2711,13 +2778,13 @@
         <v>29</v>
       </c>
       <c r="T13" t="n">
-        <v>39.8</v>
+        <v>39.9</v>
       </c>
       <c r="U13" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="V13" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W13" t="n">
         <v>7</v>
@@ -2726,22 +2793,22 @@
         <v>5.9</v>
       </c>
       <c r="Y13" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z13" t="n">
         <v>20.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>95.09999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>-8.800000000000001</v>
+        <v>-8.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE13" t="n">
         <v>28</v>
@@ -2753,7 +2820,7 @@
         <v>28</v>
       </c>
       <c r="AH13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AI13" t="n">
         <v>25</v>
@@ -2765,25 +2832,25 @@
         <v>30</v>
       </c>
       <c r="AL13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM13" t="n">
         <v>16</v>
       </c>
       <c r="AN13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO13" t="n">
         <v>29</v>
       </c>
       <c r="AP13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ13" t="n">
         <v>29</v>
       </c>
       <c r="AR13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS13" t="n">
         <v>23</v>
@@ -2798,25 +2865,25 @@
         <v>23</v>
       </c>
       <c r="AW13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX13" t="n">
         <v>3</v>
       </c>
       <c r="AY13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ13" t="n">
         <v>6</v>
       </c>
       <c r="BA13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB13" t="n">
         <v>27</v>
       </c>
       <c r="BC13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-15-2008-09</t>
+          <t>2009-04-15</t>
         </is>
       </c>
     </row>
@@ -2845,25 +2912,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E14" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F14" t="n">
         <v>17</v>
       </c>
       <c r="G14" t="n">
-        <v>0.79</v>
+        <v>0.793</v>
       </c>
       <c r="H14" t="n">
         <v>48.2</v>
       </c>
       <c r="I14" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="J14" t="n">
-        <v>85.2</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K14" t="n">
         <v>0.474</v>
@@ -2872,25 +2939,25 @@
         <v>6.7</v>
       </c>
       <c r="M14" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0.359</v>
+        <v>0.361</v>
       </c>
       <c r="O14" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="P14" t="n">
         <v>25.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.769</v>
+        <v>0.77</v>
       </c>
       <c r="R14" t="n">
         <v>12.4</v>
       </c>
       <c r="S14" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="T14" t="n">
         <v>43.9</v>
@@ -2899,7 +2966,7 @@
         <v>23.3</v>
       </c>
       <c r="V14" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="W14" t="n">
         <v>8.800000000000001</v>
@@ -2911,19 +2978,19 @@
         <v>4.8</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.1</v>
+        <v>106.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -2935,7 +3002,7 @@
         <v>2</v>
       </c>
       <c r="AH14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI14" t="n">
         <v>2</v>
@@ -2953,10 +3020,10 @@
         <v>15</v>
       </c>
       <c r="AN14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP14" t="n">
         <v>8</v>
@@ -2983,22 +3050,22 @@
         <v>2</v>
       </c>
       <c r="AX14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ14" t="n">
         <v>17</v>
       </c>
       <c r="BA14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB14" t="n">
         <v>3</v>
       </c>
       <c r="BC14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-15-2008-09</t>
+          <t>2009-04-15</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F15" t="n">
         <v>58</v>
       </c>
       <c r="G15" t="n">
-        <v>0.293</v>
+        <v>0.284</v>
       </c>
       <c r="H15" t="n">
         <v>48.3</v>
@@ -3048,13 +3115,13 @@
         <v>77</v>
       </c>
       <c r="K15" t="n">
-        <v>0.454</v>
+        <v>0.453</v>
       </c>
       <c r="L15" t="n">
         <v>4.9</v>
       </c>
       <c r="M15" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="N15" t="n">
         <v>0.36</v>
@@ -3066,19 +3133,19 @@
         <v>25.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.756</v>
+        <v>0.757</v>
       </c>
       <c r="R15" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S15" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="T15" t="n">
         <v>38.8</v>
       </c>
       <c r="U15" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="V15" t="n">
         <v>15.3</v>
@@ -3087,7 +3154,7 @@
         <v>7.5</v>
       </c>
       <c r="X15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y15" t="n">
         <v>5.4</v>
@@ -3096,25 +3163,25 @@
         <v>21.7</v>
       </c>
       <c r="AA15" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.5</v>
+        <v>-5.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH15" t="n">
         <v>14</v>
@@ -3126,7 +3193,7 @@
         <v>29</v>
       </c>
       <c r="AK15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL15" t="n">
         <v>25</v>
@@ -3135,22 +3202,22 @@
         <v>27</v>
       </c>
       <c r="AN15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO15" t="n">
         <v>13</v>
       </c>
       <c r="AP15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ15" t="n">
         <v>22</v>
       </c>
       <c r="AR15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS15" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AT15" t="n">
         <v>30</v>
@@ -3162,22 +3229,22 @@
         <v>24</v>
       </c>
       <c r="AW15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX15" t="n">
         <v>18</v>
       </c>
       <c r="AY15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA15" t="n">
         <v>9</v>
       </c>
       <c r="BB15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC15" t="n">
         <v>26</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-15-2008-09</t>
+          <t>2009-04-15</t>
         </is>
       </c>
     </row>
@@ -3209,19 +3276,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F16" t="n">
         <v>39</v>
       </c>
       <c r="G16" t="n">
-        <v>0.524</v>
+        <v>0.519</v>
       </c>
       <c r="H16" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="I16" t="n">
         <v>37</v>
@@ -3230,34 +3297,34 @@
         <v>81</v>
       </c>
       <c r="K16" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L16" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="M16" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="N16" t="n">
-        <v>0.357</v>
+        <v>0.355</v>
       </c>
       <c r="O16" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="P16" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.754</v>
+        <v>0.755</v>
       </c>
       <c r="R16" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="S16" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="T16" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="U16" t="n">
         <v>20.4</v>
@@ -3266,7 +3333,7 @@
         <v>12.5</v>
       </c>
       <c r="W16" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X16" t="n">
         <v>5.5</v>
@@ -3284,10 +3351,10 @@
         <v>98.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE16" t="n">
         <v>14</v>
@@ -3308,7 +3375,7 @@
         <v>15</v>
       </c>
       <c r="AK16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AL16" t="n">
         <v>11</v>
@@ -3317,7 +3384,7 @@
         <v>9</v>
       </c>
       <c r="AN16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO16" t="n">
         <v>27</v>
@@ -3344,7 +3411,7 @@
         <v>3</v>
       </c>
       <c r="AW16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX16" t="n">
         <v>5</v>
@@ -3356,10 +3423,10 @@
         <v>16</v>
       </c>
       <c r="BA16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC16" t="n">
         <v>14</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-15-2008-09</t>
+          <t>2009-04-15</t>
         </is>
       </c>
     </row>
@@ -3406,76 +3473,76 @@
         <v>48.2</v>
       </c>
       <c r="I17" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J17" t="n">
-        <v>82.40000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.445</v>
+        <v>0.446</v>
       </c>
       <c r="L17" t="n">
         <v>6.2</v>
       </c>
       <c r="M17" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0.362</v>
+        <v>0.363</v>
       </c>
       <c r="O17" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="P17" t="n">
         <v>25.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.781</v>
+        <v>0.78</v>
       </c>
       <c r="R17" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="S17" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="T17" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="U17" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="V17" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W17" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X17" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>24.1</v>
+        <v>24.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>99.3</v>
+        <v>99.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.9</v>
+        <v>-1</v>
       </c>
       <c r="AD17" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="AE17" t="n">
         <v>20</v>
       </c>
       <c r="AF17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG17" t="n">
         <v>20</v>
@@ -3490,7 +3557,7 @@
         <v>8</v>
       </c>
       <c r="AK17" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL17" t="n">
         <v>21</v>
@@ -3502,16 +3569,16 @@
         <v>18</v>
       </c>
       <c r="AO17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ17" t="n">
         <v>11</v>
       </c>
       <c r="AR17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS17" t="n">
         <v>24</v>
@@ -3523,10 +3590,10 @@
         <v>7</v>
       </c>
       <c r="AV17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX17" t="n">
         <v>29</v>
@@ -3544,7 +3611,7 @@
         <v>15</v>
       </c>
       <c r="BC17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-15-2008-09</t>
+          <t>2009-04-15</t>
         </is>
       </c>
     </row>
@@ -3573,46 +3640,46 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E18" t="n">
         <v>24</v>
       </c>
       <c r="F18" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G18" t="n">
-        <v>0.293</v>
+        <v>0.296</v>
       </c>
       <c r="H18" t="n">
         <v>48.3</v>
       </c>
       <c r="I18" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="J18" t="n">
-        <v>82.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>0.441</v>
+        <v>0.442</v>
       </c>
       <c r="L18" t="n">
         <v>6.6</v>
       </c>
       <c r="M18" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="N18" t="n">
-        <v>0.353</v>
+        <v>0.354</v>
       </c>
       <c r="O18" t="n">
         <v>18.3</v>
       </c>
       <c r="P18" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.769</v>
+        <v>0.77</v>
       </c>
       <c r="R18" t="n">
         <v>11.9</v>
@@ -3633,25 +3700,25 @@
         <v>6.2</v>
       </c>
       <c r="X18" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="n">
         <v>5.9</v>
       </c>
       <c r="Z18" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AA18" t="n">
         <v>20</v>
       </c>
       <c r="AB18" t="n">
-        <v>97.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC18" t="n">
         <v>-4.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
@@ -3666,7 +3733,7 @@
         <v>14</v>
       </c>
       <c r="AI18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ18" t="n">
         <v>7</v>
@@ -3699,7 +3766,7 @@
         <v>18</v>
       </c>
       <c r="AT18" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AU18" t="n">
         <v>17</v>
@@ -3717,7 +3784,7 @@
         <v>29</v>
       </c>
       <c r="AZ18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA18" t="n">
         <v>24</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-15-2008-09</t>
+          <t>2009-04-15</t>
         </is>
       </c>
     </row>
@@ -3755,34 +3822,34 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E19" t="n">
         <v>34</v>
       </c>
       <c r="F19" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G19" t="n">
-        <v>0.415</v>
+        <v>0.42</v>
       </c>
       <c r="H19" t="n">
         <v>48.4</v>
       </c>
       <c r="I19" t="n">
-        <v>35.7</v>
+        <v>35.8</v>
       </c>
       <c r="J19" t="n">
         <v>79.7</v>
       </c>
       <c r="K19" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L19" t="n">
         <v>8</v>
       </c>
       <c r="M19" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="N19" t="n">
         <v>0.376</v>
@@ -3791,25 +3858,25 @@
         <v>18.8</v>
       </c>
       <c r="P19" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.779</v>
+        <v>0.778</v>
       </c>
       <c r="R19" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="S19" t="n">
         <v>29.5</v>
       </c>
       <c r="T19" t="n">
-        <v>39.8</v>
+        <v>39.7</v>
       </c>
       <c r="U19" t="n">
         <v>20</v>
       </c>
       <c r="V19" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="W19" t="n">
         <v>6.8</v>
@@ -3821,43 +3888,43 @@
         <v>4.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="AA19" t="n">
         <v>20.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>98.09999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.4</v>
+        <v>-2.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE19" t="n">
         <v>20</v>
       </c>
       <c r="AF19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK19" t="n">
         <v>24</v>
       </c>
       <c r="AL19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM19" t="n">
         <v>3</v>
@@ -3875,13 +3942,13 @@
         <v>12</v>
       </c>
       <c r="AR19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS19" t="n">
         <v>20</v>
       </c>
       <c r="AT19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU19" t="n">
         <v>26</v>
@@ -3896,16 +3963,16 @@
         <v>16</v>
       </c>
       <c r="AY19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA19" t="n">
         <v>18</v>
       </c>
       <c r="BB19" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BC19" t="n">
         <v>21</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-15-2008-09</t>
+          <t>2009-04-15</t>
         </is>
       </c>
     </row>
@@ -3937,19 +4004,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E20" t="n">
         <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G20" t="n">
-        <v>0.598</v>
+        <v>0.605</v>
       </c>
       <c r="H20" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="I20" t="n">
         <v>35.5</v>
@@ -3964,34 +4031,34 @@
         <v>6.8</v>
       </c>
       <c r="M20" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="N20" t="n">
         <v>0.364</v>
       </c>
       <c r="O20" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="P20" t="n">
         <v>22.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="R20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="S20" t="n">
         <v>29.9</v>
       </c>
       <c r="T20" t="n">
-        <v>39.7</v>
+        <v>39.8</v>
       </c>
       <c r="U20" t="n">
         <v>19.6</v>
       </c>
       <c r="V20" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="W20" t="n">
         <v>7.2</v>
@@ -4000,7 +4067,7 @@
         <v>4.1</v>
       </c>
       <c r="Y20" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Z20" t="n">
         <v>20.3</v>
@@ -4012,22 +4079,22 @@
         <v>95.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH20" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI20" t="n">
         <v>28</v>
@@ -4036,7 +4103,7 @@
         <v>27</v>
       </c>
       <c r="AK20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL20" t="n">
         <v>13</v>
@@ -4054,7 +4121,7 @@
         <v>29</v>
       </c>
       <c r="AQ20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR20" t="n">
         <v>28</v>
@@ -4063,7 +4130,7 @@
         <v>16</v>
       </c>
       <c r="AT20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU20" t="n">
         <v>28</v>
@@ -4072,7 +4139,7 @@
         <v>4</v>
       </c>
       <c r="AW20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX20" t="n">
         <v>26</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-15-2008-09</t>
+          <t>2009-04-15</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E21" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F21" t="n">
         <v>50</v>
       </c>
       <c r="G21" t="n">
-        <v>0.39</v>
+        <v>0.383</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
@@ -4143,13 +4210,13 @@
         <v>0.445</v>
       </c>
       <c r="L21" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="M21" t="n">
         <v>27.9</v>
       </c>
       <c r="N21" t="n">
-        <v>0.36</v>
+        <v>0.361</v>
       </c>
       <c r="O21" t="n">
         <v>18.2</v>
@@ -4158,7 +4225,7 @@
         <v>23.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.784</v>
+        <v>0.783</v>
       </c>
       <c r="R21" t="n">
         <v>11.1</v>
@@ -4173,7 +4240,7 @@
         <v>21.2</v>
       </c>
       <c r="V21" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W21" t="n">
         <v>7.4</v>
@@ -4194,10 +4261,10 @@
         <v>105.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2.6</v>
+        <v>-3</v>
       </c>
       <c r="AD21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE21" t="n">
         <v>23</v>
@@ -4218,7 +4285,7 @@
         <v>1</v>
       </c>
       <c r="AK21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4230,7 +4297,7 @@
         <v>19</v>
       </c>
       <c r="AO21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP21" t="n">
         <v>22</v>
@@ -4239,13 +4306,13 @@
         <v>10</v>
       </c>
       <c r="AR21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS21" t="n">
         <v>9</v>
       </c>
       <c r="AT21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU21" t="n">
         <v>11</v>
@@ -4254,16 +4321,16 @@
         <v>18</v>
       </c>
       <c r="AW21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
@@ -4272,7 +4339,7 @@
         <v>4</v>
       </c>
       <c r="BC21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-15-2008-09</t>
+          <t>2009-04-15</t>
         </is>
       </c>
     </row>
@@ -4301,28 +4368,28 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F22" t="n">
         <v>59</v>
       </c>
       <c r="G22" t="n">
-        <v>0.28</v>
+        <v>0.272</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
       </c>
       <c r="I22" t="n">
-        <v>36.6</v>
+        <v>36.4</v>
       </c>
       <c r="J22" t="n">
-        <v>81.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="K22" t="n">
-        <v>0.447</v>
+        <v>0.445</v>
       </c>
       <c r="L22" t="n">
         <v>4</v>
@@ -4337,28 +4404,28 @@
         <v>19.8</v>
       </c>
       <c r="P22" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.786</v>
+        <v>0.785</v>
       </c>
       <c r="R22" t="n">
         <v>12.2</v>
       </c>
       <c r="S22" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="T22" t="n">
         <v>42.6</v>
       </c>
       <c r="U22" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="V22" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="W22" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X22" t="n">
         <v>4.5</v>
@@ -4373,13 +4440,13 @@
         <v>20.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>97</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC22" t="n">
-        <v>-6.1</v>
+        <v>-6.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE22" t="n">
         <v>27</v>
@@ -4394,13 +4461,13 @@
         <v>14</v>
       </c>
       <c r="AI22" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AJ22" t="n">
         <v>9</v>
       </c>
       <c r="AK22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL22" t="n">
         <v>30</v>
@@ -4412,10 +4479,10 @@
         <v>28</v>
       </c>
       <c r="AO22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ22" t="n">
         <v>9</v>
@@ -4424,19 +4491,19 @@
         <v>4</v>
       </c>
       <c r="AS22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT22" t="n">
         <v>6</v>
       </c>
       <c r="AU22" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AV22" t="n">
         <v>30</v>
       </c>
       <c r="AW22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX22" t="n">
         <v>22</v>
@@ -4445,7 +4512,7 @@
         <v>17</v>
       </c>
       <c r="AZ22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA22" t="n">
         <v>21</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-15-2008-09</t>
+          <t>2009-04-15</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E23" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F23" t="n">
         <v>23</v>
       </c>
       <c r="G23" t="n">
-        <v>0.72</v>
+        <v>0.716</v>
       </c>
       <c r="H23" t="n">
         <v>48.1</v>
@@ -4513,16 +4580,16 @@
         <v>26.2</v>
       </c>
       <c r="N23" t="n">
-        <v>0.381</v>
+        <v>0.38</v>
       </c>
       <c r="O23" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="P23" t="n">
         <v>27.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.715</v>
+        <v>0.716</v>
       </c>
       <c r="R23" t="n">
         <v>10</v>
@@ -4531,37 +4598,37 @@
         <v>33.3</v>
       </c>
       <c r="T23" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="U23" t="n">
         <v>19.4</v>
       </c>
       <c r="V23" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W23" t="n">
         <v>7</v>
       </c>
       <c r="X23" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y23" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Z23" t="n">
         <v>20.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>101</v>
+        <v>101.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4573,10 +4640,10 @@
         <v>4</v>
       </c>
       <c r="AH23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI23" t="n">
         <v>27</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>26</v>
       </c>
       <c r="AJ23" t="n">
         <v>26</v>
@@ -4594,7 +4661,7 @@
         <v>7</v>
       </c>
       <c r="AO23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP23" t="n">
         <v>4</v>
@@ -4615,10 +4682,10 @@
         <v>29</v>
       </c>
       <c r="AV23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX23" t="n">
         <v>6</v>
@@ -4633,7 +4700,7 @@
         <v>6</v>
       </c>
       <c r="BB23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC23" t="n">
         <v>4</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-15-2008-09</t>
+          <t>2009-04-15</t>
         </is>
       </c>
     </row>
@@ -4665,28 +4732,28 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E24" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F24" t="n">
         <v>41</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5</v>
+        <v>0.494</v>
       </c>
       <c r="H24" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="I24" t="n">
         <v>36.5</v>
       </c>
       <c r="J24" t="n">
-        <v>79.7</v>
+        <v>79.8</v>
       </c>
       <c r="K24" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L24" t="n">
         <v>4.2</v>
@@ -4698,13 +4765,13 @@
         <v>0.318</v>
       </c>
       <c r="O24" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="P24" t="n">
-        <v>27</v>
+        <v>26.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.745</v>
+        <v>0.746</v>
       </c>
       <c r="R24" t="n">
         <v>12.7</v>
@@ -4731,40 +4798,40 @@
         <v>4.9</v>
       </c>
       <c r="Z24" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>97.40000000000001</v>
+        <v>97.2</v>
       </c>
       <c r="AC24" t="n">
         <v>0.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ24" t="n">
         <v>18</v>
       </c>
-      <c r="AJ24" t="n">
-        <v>20</v>
-      </c>
       <c r="AK24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL24" t="n">
         <v>29</v>
@@ -4788,19 +4855,19 @@
         <v>2</v>
       </c>
       <c r="AS24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT24" t="n">
         <v>17</v>
       </c>
       <c r="AU24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX24" t="n">
         <v>12</v>
@@ -4809,10 +4876,10 @@
         <v>16</v>
       </c>
       <c r="AZ24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB24" t="n">
         <v>22</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-15-2008-09</t>
+          <t>2009-04-15</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E25" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F25" t="n">
         <v>36</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.556</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
@@ -4865,10 +4932,10 @@
         <v>41.1</v>
       </c>
       <c r="J25" t="n">
-        <v>81.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="K25" t="n">
-        <v>0.504</v>
+        <v>0.505</v>
       </c>
       <c r="L25" t="n">
         <v>6.7</v>
@@ -4877,31 +4944,31 @@
         <v>17.6</v>
       </c>
       <c r="N25" t="n">
-        <v>0.383</v>
+        <v>0.382</v>
       </c>
       <c r="O25" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="P25" t="n">
-        <v>27.5</v>
+        <v>27.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.744</v>
+        <v>0.745</v>
       </c>
       <c r="R25" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S25" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="T25" t="n">
-        <v>41.7</v>
+        <v>41.6</v>
       </c>
       <c r="U25" t="n">
         <v>23.2</v>
       </c>
       <c r="V25" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="W25" t="n">
         <v>7.2</v>
@@ -4919,13 +4986,13 @@
         <v>22.9</v>
       </c>
       <c r="AB25" t="n">
-        <v>109.4</v>
+        <v>109.3</v>
       </c>
       <c r="AC25" t="n">
         <v>1.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
         <v>13</v>
@@ -4937,13 +5004,13 @@
         <v>13</v>
       </c>
       <c r="AH25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI25" t="n">
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK25" t="n">
         <v>1</v>
@@ -4967,13 +5034,13 @@
         <v>26</v>
       </c>
       <c r="AR25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS25" t="n">
         <v>10</v>
       </c>
       <c r="AT25" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AU25" t="n">
         <v>3</v>
@@ -4985,7 +5052,7 @@
         <v>18</v>
       </c>
       <c r="AX25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY25" t="n">
         <v>10</v>
@@ -5000,7 +5067,7 @@
         <v>1</v>
       </c>
       <c r="BC25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-15-2008-09</t>
+          <t>2009-04-15</t>
         </is>
       </c>
     </row>
@@ -5032,25 +5099,25 @@
         <v>81</v>
       </c>
       <c r="E26" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F26" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G26" t="n">
-        <v>0.667</v>
+        <v>0.654</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J26" t="n">
-        <v>79.09999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="K26" t="n">
-        <v>0.466</v>
+        <v>0.464</v>
       </c>
       <c r="L26" t="n">
         <v>7.2</v>
@@ -5059,31 +5126,31 @@
         <v>18.9</v>
       </c>
       <c r="N26" t="n">
-        <v>0.383</v>
+        <v>0.38</v>
       </c>
       <c r="O26" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="P26" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.766</v>
+        <v>0.765</v>
       </c>
       <c r="R26" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="S26" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="T26" t="n">
         <v>41.7</v>
       </c>
       <c r="U26" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V26" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="W26" t="n">
         <v>6.7</v>
@@ -5098,37 +5165,37 @@
         <v>20.4</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.7</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="AE26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH26" t="n">
         <v>11</v>
       </c>
       <c r="AI26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ26" t="n">
         <v>23</v>
       </c>
       <c r="AK26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL26" t="n">
         <v>9</v>
@@ -5137,10 +5204,10 @@
         <v>12</v>
       </c>
       <c r="AN26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AO26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AP26" t="n">
         <v>16</v>
@@ -5158,7 +5225,7 @@
         <v>13</v>
       </c>
       <c r="AU26" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AV26" t="n">
         <v>8</v>
@@ -5173,7 +5240,7 @@
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA26" t="n">
         <v>11</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-15-2008-09</t>
+          <t>2009-04-15</t>
         </is>
       </c>
     </row>
@@ -5211,25 +5278,25 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F27" t="n">
         <v>65</v>
       </c>
       <c r="G27" t="n">
-        <v>0.207</v>
+        <v>0.198</v>
       </c>
       <c r="H27" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I27" t="n">
         <v>36.5</v>
       </c>
       <c r="J27" t="n">
-        <v>81.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K27" t="n">
         <v>0.447</v>
@@ -5238,10 +5305,10 @@
         <v>7.1</v>
       </c>
       <c r="M27" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="N27" t="n">
-        <v>0.368</v>
+        <v>0.367</v>
       </c>
       <c r="O27" t="n">
         <v>20.5</v>
@@ -5256,13 +5323,13 @@
         <v>10.2</v>
       </c>
       <c r="S27" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="T27" t="n">
         <v>39.1</v>
       </c>
       <c r="U27" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="V27" t="n">
         <v>15.4</v>
@@ -5271,7 +5338,7 @@
         <v>6.9</v>
       </c>
       <c r="X27" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y27" t="n">
         <v>5.2</v>
@@ -5280,16 +5347,16 @@
         <v>23.3</v>
       </c>
       <c r="AA27" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB27" t="n">
         <v>100.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>-8.800000000000001</v>
+        <v>-9</v>
       </c>
       <c r="AD27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE27" t="n">
         <v>30</v>
@@ -5304,10 +5371,10 @@
         <v>4</v>
       </c>
       <c r="AI27" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AJ27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK27" t="n">
         <v>25</v>
@@ -5319,7 +5386,7 @@
         <v>11</v>
       </c>
       <c r="AN27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO27" t="n">
         <v>4</v>
@@ -5331,7 +5398,7 @@
         <v>6</v>
       </c>
       <c r="AR27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS27" t="n">
         <v>25</v>
@@ -5352,7 +5419,7 @@
         <v>25</v>
       </c>
       <c r="AY27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ27" t="n">
         <v>29</v>
@@ -5364,7 +5431,7 @@
         <v>12</v>
       </c>
       <c r="BC27" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-15-2008-09</t>
+          <t>2009-04-15</t>
         </is>
       </c>
     </row>
@@ -5393,28 +5460,28 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E28" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F28" t="n">
         <v>28</v>
       </c>
       <c r="G28" t="n">
-        <v>0.659</v>
+        <v>0.654</v>
       </c>
       <c r="H28" t="n">
         <v>48.5</v>
       </c>
       <c r="I28" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J28" t="n">
-        <v>79.7</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.466</v>
+        <v>0.465</v>
       </c>
       <c r="L28" t="n">
         <v>7.6</v>
@@ -5423,7 +5490,7 @@
         <v>19.8</v>
       </c>
       <c r="N28" t="n">
-        <v>0.386</v>
+        <v>0.387</v>
       </c>
       <c r="O28" t="n">
         <v>15.2</v>
@@ -5438,7 +5505,7 @@
         <v>8.9</v>
       </c>
       <c r="S28" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="T28" t="n">
         <v>41</v>
@@ -5459,7 +5526,7 @@
         <v>4.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AA28" t="n">
         <v>18.4</v>
@@ -5468,13 +5535,13 @@
         <v>97</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF28" t="n">
         <v>6</v>
@@ -5483,16 +5550,16 @@
         <v>6</v>
       </c>
       <c r="AH28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI28" t="n">
         <v>12</v>
       </c>
       <c r="AJ28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL28" t="n">
         <v>6</v>
@@ -5519,7 +5586,7 @@
         <v>4</v>
       </c>
       <c r="AT28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU28" t="n">
         <v>12</v>
@@ -5534,7 +5601,7 @@
         <v>27</v>
       </c>
       <c r="AY28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5546,7 +5613,7 @@
         <v>23</v>
       </c>
       <c r="BC28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-15-2008-09</t>
+          <t>2009-04-15</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E29" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F29" t="n">
         <v>49</v>
       </c>
       <c r="G29" t="n">
-        <v>0.402</v>
+        <v>0.395</v>
       </c>
       <c r="H29" t="n">
         <v>48.3</v>
@@ -5593,19 +5660,19 @@
         <v>37.2</v>
       </c>
       <c r="J29" t="n">
-        <v>81.40000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="K29" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L29" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="M29" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="N29" t="n">
-        <v>0.372</v>
+        <v>0.371</v>
       </c>
       <c r="O29" t="n">
         <v>18.7</v>
@@ -5617,16 +5684,16 @@
         <v>0.824</v>
       </c>
       <c r="R29" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S29" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="T29" t="n">
-        <v>40.4</v>
+        <v>40.2</v>
       </c>
       <c r="U29" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="V29" t="n">
         <v>13.4</v>
@@ -5647,13 +5714,13 @@
         <v>20.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>99</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC29" t="n">
-        <v>-2.8</v>
+        <v>-3</v>
       </c>
       <c r="AD29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE29" t="n">
         <v>22</v>
@@ -5680,10 +5747,10 @@
         <v>24</v>
       </c>
       <c r="AM29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO29" t="n">
         <v>16</v>
@@ -5695,16 +5762,16 @@
         <v>1</v>
       </c>
       <c r="AR29" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT29" t="n">
         <v>21</v>
       </c>
       <c r="AU29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV29" t="n">
         <v>10</v>
@@ -5713,7 +5780,7 @@
         <v>27</v>
       </c>
       <c r="AX29" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AY29" t="n">
         <v>12</v>
@@ -5728,7 +5795,7 @@
         <v>16</v>
       </c>
       <c r="BC29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-15-2008-09</t>
+          <t>2009-04-15</t>
         </is>
       </c>
     </row>
@@ -5847,7 +5914,7 @@
         <v>11</v>
       </c>
       <c r="AH30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AI30" t="n">
         <v>6</v>
@@ -5865,7 +5932,7 @@
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO30" t="n">
         <v>3</v>
@@ -5883,7 +5950,7 @@
         <v>19</v>
       </c>
       <c r="AT30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU30" t="n">
         <v>1</v>
@@ -5898,7 +5965,7 @@
         <v>21</v>
       </c>
       <c r="AY30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ30" t="n">
         <v>23</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-15-2008-09</t>
+          <t>2009-04-15</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E31" t="n">
         <v>19</v>
       </c>
       <c r="F31" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G31" t="n">
-        <v>0.232</v>
+        <v>0.235</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
@@ -5960,25 +6027,25 @@
         <v>81.2</v>
       </c>
       <c r="K31" t="n">
-        <v>0.45</v>
+        <v>0.449</v>
       </c>
       <c r="L31" t="n">
         <v>4.8</v>
       </c>
       <c r="M31" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0.33</v>
+        <v>0.329</v>
       </c>
       <c r="O31" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="P31" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.767</v>
+        <v>0.766</v>
       </c>
       <c r="R31" t="n">
         <v>11.7</v>
@@ -5990,7 +6057,7 @@
         <v>40.1</v>
       </c>
       <c r="U31" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="V31" t="n">
         <v>14</v>
@@ -5999,25 +6066,25 @@
         <v>7.5</v>
       </c>
       <c r="X31" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y31" t="n">
         <v>5.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AA31" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AB31" t="n">
-        <v>96.09999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC31" t="n">
         <v>-7.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE31" t="n">
         <v>28</v>
@@ -6032,7 +6099,7 @@
         <v>29</v>
       </c>
       <c r="AI31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ31" t="n">
         <v>14</v>
@@ -6050,7 +6117,7 @@
         <v>29</v>
       </c>
       <c r="AO31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP31" t="n">
         <v>20</v>
@@ -6062,7 +6129,7 @@
         <v>8</v>
       </c>
       <c r="AS31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT31" t="n">
         <v>22</v>
@@ -6071,10 +6138,10 @@
         <v>25</v>
       </c>
       <c r="AV31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX31" t="n">
         <v>23</v>
@@ -6083,7 +6150,7 @@
         <v>22</v>
       </c>
       <c r="AZ31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA31" t="n">
         <v>25</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-15-2008-09</t>
+          <t>2009-04-15</t>
         </is>
       </c>
     </row>
